--- a/analiza-svetilki/izlez/Проверка_мерни_места.xlsx
+++ b/analiza-svetilki/izlez/Проверка_мерни_места.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Листи" sheetId="5" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Препознаени'!$A$1:$K$227</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Препознаени'!$A$1:$N$227</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Населени места'!$A$1:$I$80</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -519,12 +519,43 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Населено место = службено име од списокот на 79 населени места.</t>
+          <t>Последните три колони покажуваат како троши мерното место (пресметка од месечните kWh):</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Ноќна моќност kW – дел што расте и опаѓа со должината на ноќта (светилки).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Постојана моќност kW – дел што троши и дење, 24 часа (светилки што светат дење или друг потрошувач на ормарот).</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Профил: ноќен / мешан / постојан. Мерните места со постојан профил веројатно не се само улично осветлување: проверете ги.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Населено место = службено име од списокот на 79 населени места.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Единица = населените места Горно/Долно и Големо/Мало се обединети по основното име; Гарани и Стрелци се заедно.</t>
         </is>
@@ -541,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K227"/>
+  <dimension ref="A1:N227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -555,6 +586,9 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="26" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -613,6 +647,21 @@
           <t>Забелешка</t>
         </is>
       </c>
+      <c r="L1" s="2" t="inlineStr">
+        <is>
+          <t>Ноќна моќност kW</t>
+        </is>
+      </c>
+      <c r="M1" s="2" t="inlineStr">
+        <is>
+          <t>Постојана моќност kW</t>
+        </is>
+      </c>
+      <c r="N1" s="2" t="inlineStr">
+        <is>
+          <t>Профил</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -653,6 +702,17 @@
       <c r="H2" t="n">
         <v>2165</v>
       </c>
+      <c r="L2" t="n">
+        <v>0.497</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -693,6 +753,17 @@
       <c r="H3" t="n">
         <v>479</v>
       </c>
+      <c r="L3" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -733,6 +804,17 @@
       <c r="H4" t="n">
         <v>4602</v>
       </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -773,6 +855,17 @@
       <c r="H5" t="n">
         <v>3947</v>
       </c>
+      <c r="L5" t="n">
+        <v>0.909</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -813,6 +906,17 @@
       <c r="H6" t="n">
         <v>16341</v>
       </c>
+      <c r="L6" t="n">
+        <v>3.667</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -853,6 +957,17 @@
       <c r="H7" t="n">
         <v>4988</v>
       </c>
+      <c r="L7" t="n">
+        <v>1.145</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -893,6 +1008,17 @@
       <c r="H8" t="n">
         <v>8073</v>
       </c>
+      <c r="L8" t="n">
+        <v>1.764</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -933,6 +1059,17 @@
       <c r="H9" t="n">
         <v>2211</v>
       </c>
+      <c r="L9" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -973,6 +1110,17 @@
       <c r="H10" t="n">
         <v>3179</v>
       </c>
+      <c r="L10" t="n">
+        <v>0.734</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1013,6 +1161,17 @@
       <c r="H11" t="n">
         <v>9014</v>
       </c>
+      <c r="L11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1053,6 +1212,17 @@
       <c r="H12" t="n">
         <v>39</v>
       </c>
+      <c r="L12" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1093,6 +1263,17 @@
       <c r="H13" t="n">
         <v>12145</v>
       </c>
+      <c r="L13" t="n">
+        <v>2.767</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -1129,6 +1310,17 @@
       <c r="H14" s="3" t="n">
         <v>5175</v>
       </c>
+      <c r="L14" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1169,6 +1361,17 @@
       <c r="H15" t="n">
         <v>3466</v>
       </c>
+      <c r="L15" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1209,6 +1412,17 @@
       <c r="H16" t="n">
         <v>503</v>
       </c>
+      <c r="L16" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1249,6 +1463,17 @@
       <c r="H17" t="n">
         <v>3185</v>
       </c>
+      <c r="L17" t="n">
+        <v>0.726</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1289,6 +1514,17 @@
       <c r="H18" t="n">
         <v>7863</v>
       </c>
+      <c r="L18" t="n">
+        <v>1.621</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1329,6 +1565,17 @@
       <c r="H19" t="n">
         <v>4198</v>
       </c>
+      <c r="L19" t="n">
+        <v>0.648</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1365,6 +1612,17 @@
       <c r="H20" t="n">
         <v>3966</v>
       </c>
+      <c r="L20" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1405,6 +1663,17 @@
       <c r="H21" t="n">
         <v>3854</v>
       </c>
+      <c r="L21" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1445,6 +1714,17 @@
       <c r="H22" t="n">
         <v>3611</v>
       </c>
+      <c r="L22" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1485,6 +1765,17 @@
       <c r="H23" t="n">
         <v>1749</v>
       </c>
+      <c r="L23" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1525,6 +1816,17 @@
       <c r="H24" t="n">
         <v>1397</v>
       </c>
+      <c r="L24" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1565,6 +1867,17 @@
       <c r="H25" t="n">
         <v>2954</v>
       </c>
+      <c r="L25" t="n">
+        <v>0.668</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1605,6 +1918,17 @@
       <c r="H26" t="n">
         <v>6227</v>
       </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1645,6 +1969,17 @@
       <c r="H27" t="n">
         <v>2524</v>
       </c>
+      <c r="L27" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.149</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1685,6 +2020,17 @@
       <c r="H28" t="n">
         <v>9637</v>
       </c>
+      <c r="L28" t="n">
+        <v>2.314</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1725,6 +2071,17 @@
       <c r="H29" t="n">
         <v>3370</v>
       </c>
+      <c r="L29" t="n">
+        <v>0.763</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1765,6 +2122,17 @@
       <c r="H30" t="n">
         <v>2984</v>
       </c>
+      <c r="L30" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1801,6 +2169,17 @@
       <c r="H31" t="n">
         <v>3809</v>
       </c>
+      <c r="L31" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1837,6 +2216,17 @@
       <c r="H32" t="n">
         <v>2634</v>
       </c>
+      <c r="L32" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1877,6 +2267,17 @@
       <c r="H33" t="n">
         <v>1444</v>
       </c>
+      <c r="L33" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1917,6 +2318,17 @@
       <c r="H34" t="n">
         <v>5940</v>
       </c>
+      <c r="L34" t="n">
+        <v>1.322</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1957,6 +2369,17 @@
       <c r="H35" t="n">
         <v>218</v>
       </c>
+      <c r="L35" t="n">
+        <v>0.051</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1997,6 +2420,17 @@
       <c r="H36" t="n">
         <v>9599</v>
       </c>
+      <c r="L36" t="n">
+        <v>2.042</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2033,6 +2467,17 @@
       <c r="H37" t="n">
         <v>9452</v>
       </c>
+      <c r="L37" t="n">
+        <v>1.348</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2073,6 +2518,17 @@
       <c r="H38" t="n">
         <v>12348</v>
       </c>
+      <c r="L38" t="n">
+        <v>2.848</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2113,6 +2569,17 @@
       <c r="H39" t="n">
         <v>3001</v>
       </c>
+      <c r="L39" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2149,6 +2616,17 @@
       <c r="H40" t="n">
         <v>7740</v>
       </c>
+      <c r="L40" t="n">
+        <v>1.647</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2189,6 +2667,17 @@
       <c r="H41" t="n">
         <v>9256</v>
       </c>
+      <c r="L41" t="n">
+        <v>2.118</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2229,6 +2718,17 @@
       <c r="H42" t="n">
         <v>804</v>
       </c>
+      <c r="L42" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2269,6 +2769,17 @@
       <c r="H43" t="n">
         <v>7825</v>
       </c>
+      <c r="L43" t="n">
+        <v>1.805</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2305,6 +2816,17 @@
       <c r="H44" t="n">
         <v>5374</v>
       </c>
+      <c r="L44" t="n">
+        <v>1.223</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2341,6 +2863,17 @@
       <c r="H45" t="n">
         <v>5414</v>
       </c>
+      <c r="L45" t="n">
+        <v>1.159</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2381,6 +2914,17 @@
       <c r="H46" t="n">
         <v>3860</v>
       </c>
+      <c r="L46" t="n">
+        <v>0.894</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2421,6 +2965,17 @@
       <c r="H47" t="n">
         <v>6933</v>
       </c>
+      <c r="L47" t="n">
+        <v>1.585</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2461,6 +3016,17 @@
       <c r="H48" t="n">
         <v>13867</v>
       </c>
+      <c r="L48" t="n">
+        <v>2.888</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2501,6 +3067,17 @@
       <c r="H49" t="n">
         <v>1137</v>
       </c>
+      <c r="L49" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2537,6 +3114,17 @@
       <c r="H50" t="n">
         <v>5626</v>
       </c>
+      <c r="L50" t="n">
+        <v>1.285</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2573,6 +3161,17 @@
       <c r="H51" t="n">
         <v>6716</v>
       </c>
+      <c r="L51" t="n">
+        <v>1.549</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2613,6 +3212,17 @@
       <c r="H52" t="n">
         <v>2049</v>
       </c>
+      <c r="L52" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2653,6 +3263,17 @@
       <c r="H53" t="n">
         <v>4139</v>
       </c>
+      <c r="L53" t="n">
+        <v>0.847</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2693,6 +3314,17 @@
       <c r="H54" t="n">
         <v>1633</v>
       </c>
+      <c r="L54" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2733,6 +3365,17 @@
       <c r="H55" t="n">
         <v>7031</v>
       </c>
+      <c r="L55" t="n">
+        <v>1.603</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2773,6 +3416,17 @@
       <c r="H56" t="n">
         <v>4984</v>
       </c>
+      <c r="L56" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2813,6 +3467,17 @@
       <c r="H57" t="n">
         <v>4639</v>
       </c>
+      <c r="L57" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2853,6 +3518,17 @@
       <c r="H58" t="n">
         <v>1056</v>
       </c>
+      <c r="L58" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.112</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2893,6 +3569,17 @@
       <c r="H59" t="n">
         <v>5678</v>
       </c>
+      <c r="L59" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2933,6 +3620,17 @@
       <c r="H60" t="n">
         <v>17618</v>
       </c>
+      <c r="L60" t="n">
+        <v>4.008</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2973,6 +3671,17 @@
       <c r="H61" t="n">
         <v>6817</v>
       </c>
+      <c r="L61" t="n">
+        <v>1.539</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3013,6 +3722,17 @@
       <c r="H62" t="n">
         <v>6570</v>
       </c>
+      <c r="L62" t="n">
+        <v>1.472</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3053,6 +3773,17 @@
       <c r="H63" t="n">
         <v>6660</v>
       </c>
+      <c r="L63" t="n">
+        <v>1.537</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3093,6 +3824,17 @@
       <c r="H64" t="n">
         <v>7678</v>
       </c>
+      <c r="L64" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3129,6 +3871,17 @@
       <c r="H65" t="n">
         <v>9196</v>
       </c>
+      <c r="L65" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3165,6 +3918,17 @@
       <c r="H66" t="n">
         <v>2967</v>
       </c>
+      <c r="L66" t="n">
+        <v>0.678</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3205,6 +3969,17 @@
       <c r="H67" t="n">
         <v>2151</v>
       </c>
+      <c r="L67" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -3245,6 +4020,17 @@
       <c r="H68" t="n">
         <v>2088</v>
       </c>
+      <c r="L68" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3281,6 +4067,17 @@
       <c r="H69" t="n">
         <v>12940</v>
       </c>
+      <c r="L69" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" t="n">
+        <v>1.283</v>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3321,6 +4118,17 @@
       <c r="H70" t="n">
         <v>9350</v>
       </c>
+      <c r="L70" t="n">
+        <v>1.603</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3357,6 +4165,17 @@
       <c r="H71" t="n">
         <v>2887</v>
       </c>
+      <c r="L71" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3397,6 +4216,17 @@
       <c r="H72" t="n">
         <v>18595</v>
       </c>
+      <c r="L72" t="n">
+        <v>1.587</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1.329</v>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3433,6 +4263,17 @@
       <c r="H73" t="n">
         <v>6179</v>
       </c>
+      <c r="L73" t="n">
+        <v>1.353</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0</v>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3473,6 +4314,17 @@
       <c r="H74" t="n">
         <v>65</v>
       </c>
+      <c r="L74" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3513,6 +4365,17 @@
       <c r="H75" t="n">
         <v>9335</v>
       </c>
+      <c r="L75" t="n">
+        <v>2.155</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0</v>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3553,6 +4416,17 @@
       <c r="H76" t="n">
         <v>1048</v>
       </c>
+      <c r="L76" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0</v>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3593,6 +4467,17 @@
       <c r="H77" t="n">
         <v>5772</v>
       </c>
+      <c r="L77" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0</v>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
@@ -3633,6 +4518,17 @@
       <c r="H78" s="3" t="n">
         <v>2253</v>
       </c>
+      <c r="L78" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -3673,6 +4569,17 @@
       <c r="H79" s="3" t="n">
         <v>3771</v>
       </c>
+      <c r="L79" t="n">
+        <v>0.869</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0</v>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3713,6 +4620,17 @@
       <c r="H80" t="n">
         <v>2995</v>
       </c>
+      <c r="L80" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0</v>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3753,6 +4671,17 @@
       <c r="H81" t="n">
         <v>3642</v>
       </c>
+      <c r="L81" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3793,6 +4722,17 @@
       <c r="H82" t="n">
         <v>3941</v>
       </c>
+      <c r="L82" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0</v>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3833,6 +4773,17 @@
       <c r="H83" t="n">
         <v>5281</v>
       </c>
+      <c r="L83" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3873,6 +4824,17 @@
       <c r="H84" t="n">
         <v>2688</v>
       </c>
+      <c r="L84" t="n">
+        <v>0.579</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3913,6 +4875,17 @@
       <c r="H85" t="n">
         <v>6967</v>
       </c>
+      <c r="L85" t="n">
+        <v>1.611</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0</v>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3953,6 +4926,17 @@
       <c r="H86" t="n">
         <v>6460</v>
       </c>
+      <c r="L86" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0</v>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3993,6 +4977,17 @@
       <c r="H87" t="n">
         <v>7856</v>
       </c>
+      <c r="L87" t="n">
+        <v>1.788</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4029,6 +5024,17 @@
       <c r="H88" t="n">
         <v>12365</v>
       </c>
+      <c r="L88" t="n">
+        <v>2.184</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4069,6 +5075,17 @@
       <c r="H89" t="n">
         <v>2483</v>
       </c>
+      <c r="L89" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4109,6 +5126,17 @@
       <c r="H90" t="n">
         <v>1336</v>
       </c>
+      <c r="L90" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4149,6 +5177,17 @@
       <c r="H91" t="n">
         <v>576</v>
       </c>
+      <c r="L91" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4185,6 +5224,17 @@
       <c r="H92" t="n">
         <v>4979</v>
       </c>
+      <c r="L92" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4225,6 +5275,17 @@
       <c r="H93" t="n">
         <v>1271</v>
       </c>
+      <c r="L93" t="n">
+        <v>0.273</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -4265,6 +5326,17 @@
       <c r="H94" t="n">
         <v>867</v>
       </c>
+      <c r="L94" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4305,6 +5377,17 @@
       <c r="H95" t="n">
         <v>1994</v>
       </c>
+      <c r="L95" t="n">
+        <v>0</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
@@ -4345,6 +5428,17 @@
       <c r="H96" s="3" t="n">
         <v>2743</v>
       </c>
+      <c r="L96" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -4385,6 +5479,17 @@
       <c r="H97" t="n">
         <v>5506</v>
       </c>
+      <c r="L97" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4425,6 +5530,17 @@
       <c r="H98" t="n">
         <v>297</v>
       </c>
+      <c r="L98" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.034</v>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4465,6 +5581,17 @@
       <c r="H99" t="n">
         <v>2365</v>
       </c>
+      <c r="L99" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4505,6 +5632,17 @@
       <c r="H100" t="n">
         <v>1370</v>
       </c>
+      <c r="L100" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.031</v>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4545,6 +5683,17 @@
       <c r="H101" t="n">
         <v>2879</v>
       </c>
+      <c r="L101" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4585,6 +5734,17 @@
       <c r="H102" t="n">
         <v>4277</v>
       </c>
+      <c r="L102" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4625,6 +5785,17 @@
       <c r="H103" t="n">
         <v>3764</v>
       </c>
+      <c r="L103" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4665,6 +5836,17 @@
       <c r="H104" t="n">
         <v>3192</v>
       </c>
+      <c r="L104" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4705,6 +5887,17 @@
       <c r="H105" t="n">
         <v>2732</v>
       </c>
+      <c r="L105" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4745,6 +5938,17 @@
       <c r="H106" t="n">
         <v>1246</v>
       </c>
+      <c r="L106" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4781,6 +5985,17 @@
       <c r="H107" t="n">
         <v>1673</v>
       </c>
+      <c r="L107" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4817,6 +6032,17 @@
       <c r="H108" t="n">
         <v>3737</v>
       </c>
+      <c r="L108" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4853,6 +6079,17 @@
       <c r="H109" t="n">
         <v>895</v>
       </c>
+      <c r="L109" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4893,6 +6130,17 @@
       <c r="H110" t="n">
         <v>4912</v>
       </c>
+      <c r="L110" t="n">
+        <v>0.836</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0.139</v>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4933,6 +6181,17 @@
       <c r="H111" t="n">
         <v>2090</v>
       </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4973,6 +6232,17 @@
       <c r="H112" t="n">
         <v>1411</v>
       </c>
+      <c r="L112" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0</v>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5013,6 +6283,17 @@
       <c r="H113" t="n">
         <v>460</v>
       </c>
+      <c r="L113" t="n">
+        <v>0.108</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0</v>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5053,6 +6334,17 @@
       <c r="H114" t="n">
         <v>2649</v>
       </c>
+      <c r="L114" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5093,6 +6385,17 @@
       <c r="H115" t="n">
         <v>2998</v>
       </c>
+      <c r="L115" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -5133,6 +6436,17 @@
       <c r="H116" s="3" t="n">
         <v>2399</v>
       </c>
+      <c r="L116" t="n">
+        <v>0.578</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5173,6 +6487,17 @@
       <c r="H117" t="n">
         <v>4225</v>
       </c>
+      <c r="L117" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5209,6 +6534,17 @@
       <c r="H118" t="n">
         <v>3797</v>
       </c>
+      <c r="L118" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5249,6 +6585,17 @@
       <c r="H119" t="n">
         <v>2776</v>
       </c>
+      <c r="L119" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
@@ -5289,6 +6636,17 @@
       <c r="H120" s="3" t="n">
         <v>3457</v>
       </c>
+      <c r="L120" t="n">
+        <v>0.593</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5329,6 +6687,17 @@
       <c r="H121" t="n">
         <v>2384</v>
       </c>
+      <c r="L121" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5369,6 +6738,17 @@
       <c r="H122" t="n">
         <v>6945</v>
       </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5405,6 +6785,17 @@
       <c r="H123" t="n">
         <v>2919</v>
       </c>
+      <c r="L123" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5441,6 +6832,17 @@
       <c r="H124" t="n">
         <v>6676</v>
       </c>
+      <c r="L124" t="n">
+        <v>1.523</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5481,6 +6883,17 @@
       <c r="H125" t="n">
         <v>10431</v>
       </c>
+      <c r="L125" t="n">
+        <v>2.421</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5521,6 +6934,17 @@
       <c r="H126" t="n">
         <v>4014</v>
       </c>
+      <c r="L126" t="n">
+        <v>0.885</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5557,6 +6981,17 @@
       <c r="H127" t="n">
         <v>2614</v>
       </c>
+      <c r="L127" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5597,6 +7032,17 @@
       <c r="H128" t="n">
         <v>3700</v>
       </c>
+      <c r="L128" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5637,6 +7083,17 @@
       <c r="H129" t="n">
         <v>3062</v>
       </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5673,6 +7130,17 @@
       <c r="H130" t="n">
         <v>7507</v>
       </c>
+      <c r="L130" t="n">
+        <v>1.441</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5713,6 +7181,17 @@
       <c r="H131" t="n">
         <v>1287</v>
       </c>
+      <c r="L131" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5753,6 +7232,17 @@
       <c r="H132" t="n">
         <v>4880</v>
       </c>
+      <c r="L132" t="n">
+        <v>1.117</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5793,6 +7283,17 @@
       <c r="H133" t="n">
         <v>2110</v>
       </c>
+      <c r="L133" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0</v>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5833,6 +7334,17 @@
       <c r="H134" t="n">
         <v>3667</v>
       </c>
+      <c r="L134" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5869,6 +7381,17 @@
       <c r="H135" t="n">
         <v>2019</v>
       </c>
+      <c r="L135" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0</v>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5909,6 +7432,17 @@
       <c r="H136" t="n">
         <v>2601</v>
       </c>
+      <c r="L136" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5945,6 +7479,17 @@
       <c r="H137" t="n">
         <v>933</v>
       </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5981,6 +7526,17 @@
       <c r="H138" t="n">
         <v>6684</v>
       </c>
+      <c r="L138" t="n">
+        <v>1.202</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6017,6 +7573,17 @@
       <c r="H139" t="n">
         <v>13152</v>
       </c>
+      <c r="L139" t="n">
+        <v>2.762</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6057,6 +7624,17 @@
       <c r="H140" t="n">
         <v>7006</v>
       </c>
+      <c r="L140" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6097,6 +7675,17 @@
       <c r="H141" t="n">
         <v>6410</v>
       </c>
+      <c r="L141" t="n">
+        <v>1.438</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0</v>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6137,6 +7726,17 @@
       <c r="H142" t="n">
         <v>13487</v>
       </c>
+      <c r="L142" t="n">
+        <v>2.557</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6177,6 +7777,17 @@
       <c r="H143" t="n">
         <v>3326</v>
       </c>
+      <c r="L143" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -6217,6 +7828,17 @@
       <c r="H144" t="n">
         <v>12237</v>
       </c>
+      <c r="L144" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="M144" t="n">
+        <v>0.124</v>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -6257,6 +7879,17 @@
       <c r="H145" t="n">
         <v>2411</v>
       </c>
+      <c r="L145" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M145" t="n">
+        <v>0.041</v>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -6297,6 +7930,17 @@
       <c r="H146" t="n">
         <v>1330</v>
       </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -6337,6 +7981,17 @@
       <c r="H147" t="n">
         <v>7047</v>
       </c>
+      <c r="L147" t="n">
+        <v>1.445</v>
+      </c>
+      <c r="M147" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -6377,6 +8032,17 @@
       <c r="H148" t="n">
         <v>4285</v>
       </c>
+      <c r="L148" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="M148" t="n">
+        <v>0</v>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -6417,6 +8083,17 @@
       <c r="H149" t="n">
         <v>4250</v>
       </c>
+      <c r="L149" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="M149" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -6453,6 +8130,17 @@
       <c r="H150" t="n">
         <v>7162</v>
       </c>
+      <c r="L150" t="n">
+        <v>1.545</v>
+      </c>
+      <c r="M150" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -6493,6 +8181,17 @@
       <c r="H151" t="n">
         <v>8192</v>
       </c>
+      <c r="L151" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="M151" t="n">
+        <v>0</v>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -6533,6 +8232,17 @@
       <c r="H152" t="n">
         <v>4182</v>
       </c>
+      <c r="L152" t="n">
+        <v>0.881</v>
+      </c>
+      <c r="M152" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -6573,6 +8283,17 @@
       <c r="H153" t="n">
         <v>2</v>
       </c>
+      <c r="L153" t="n">
+        <v>0</v>
+      </c>
+      <c r="M153" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -6613,6 +8334,17 @@
       <c r="H154" t="n">
         <v>6257</v>
       </c>
+      <c r="L154" t="n">
+        <v>1.452</v>
+      </c>
+      <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -6653,6 +8385,17 @@
       <c r="H155" t="n">
         <v>8012</v>
       </c>
+      <c r="L155" t="n">
+        <v>1.692</v>
+      </c>
+      <c r="M155" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6693,6 +8436,17 @@
       <c r="H156" t="n">
         <v>541</v>
       </c>
+      <c r="L156" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="M156" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6729,6 +8483,17 @@
       <c r="H157" t="n">
         <v>2148</v>
       </c>
+      <c r="L157" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="M157" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6769,6 +8534,17 @@
       <c r="H158" t="n">
         <v>3956</v>
       </c>
+      <c r="L158" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -6809,6 +8585,17 @@
       <c r="H159" s="3" t="n">
         <v>2752</v>
       </c>
+      <c r="L159" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" t="n">
+        <v>0.384</v>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6849,6 +8636,17 @@
       <c r="H160" t="n">
         <v>2409</v>
       </c>
+      <c r="L160" t="n">
+        <v>0.555</v>
+      </c>
+      <c r="M160" t="n">
+        <v>0</v>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6889,6 +8687,17 @@
       <c r="H161" t="n">
         <v>5037</v>
       </c>
+      <c r="L161" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6925,6 +8734,17 @@
       <c r="H162" t="n">
         <v>1731</v>
       </c>
+      <c r="L162" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M162" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6961,6 +8781,17 @@
       <c r="H163" t="n">
         <v>4109</v>
       </c>
+      <c r="L163" t="n">
+        <v>0.947</v>
+      </c>
+      <c r="M163" t="n">
+        <v>0</v>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -7001,6 +8832,17 @@
       <c r="H164" t="n">
         <v>1299</v>
       </c>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -7041,6 +8883,17 @@
       <c r="H165" t="n">
         <v>437</v>
       </c>
+      <c r="L165" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="M165" t="n">
+        <v>0</v>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -7081,6 +8934,17 @@
       <c r="H166" t="n">
         <v>9</v>
       </c>
+      <c r="L166" t="n">
+        <v>0</v>
+      </c>
+      <c r="M166" t="n">
+        <v>0</v>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -7117,6 +8981,17 @@
       <c r="H167" t="n">
         <v>369</v>
       </c>
+      <c r="L167" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="M167" t="n">
+        <v>0</v>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -7157,6 +9032,17 @@
       <c r="H168" t="n">
         <v>1091</v>
       </c>
+      <c r="L168" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="M168" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -7197,6 +9083,17 @@
       <c r="H169" t="n">
         <v>3825</v>
       </c>
+      <c r="L169" t="n">
+        <v>0.792</v>
+      </c>
+      <c r="M169" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -7237,6 +9134,17 @@
       <c r="H170" t="n">
         <v>1529</v>
       </c>
+      <c r="L170" t="n">
+        <v>0</v>
+      </c>
+      <c r="M170" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -7277,6 +9185,17 @@
       <c r="H171" t="n">
         <v>8</v>
       </c>
+      <c r="L171" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="M171" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -7317,6 +9236,17 @@
       <c r="H172" t="n">
         <v>332</v>
       </c>
+      <c r="L172" t="n">
+        <v>0</v>
+      </c>
+      <c r="M172" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -7353,6 +9283,17 @@
       <c r="H173" t="n">
         <v>680</v>
       </c>
+      <c r="L173" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="M173" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -7389,6 +9330,17 @@
       <c r="H174" t="n">
         <v>538</v>
       </c>
+      <c r="L174" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -7429,6 +9381,17 @@
       <c r="H175" t="n">
         <v>155</v>
       </c>
+      <c r="L175" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="M175" t="n">
+        <v>0</v>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -7465,6 +9428,17 @@
       <c r="H176" t="n">
         <v>760</v>
       </c>
+      <c r="L176" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="M176" t="n">
+        <v>0</v>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -7505,6 +9479,17 @@
       <c r="H177" t="n">
         <v>4858</v>
       </c>
+      <c r="L177" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="M177" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -7541,6 +9526,17 @@
       <c r="H178" t="n">
         <v>3834</v>
       </c>
+      <c r="L178" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="M178" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -7581,6 +9577,17 @@
       <c r="H179" t="n">
         <v>3769</v>
       </c>
+      <c r="L179" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="M179" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -7621,6 +9628,17 @@
       <c r="H180" t="n">
         <v>4502</v>
       </c>
+      <c r="L180" t="n">
+        <v>0.877</v>
+      </c>
+      <c r="M180" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -7661,6 +9679,17 @@
       <c r="H181" t="n">
         <v>10204</v>
       </c>
+      <c r="L181" t="n">
+        <v>2.369</v>
+      </c>
+      <c r="M181" t="n">
+        <v>0</v>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -7697,6 +9726,17 @@
       <c r="H182" t="n">
         <v>6117</v>
       </c>
+      <c r="L182" t="n">
+        <v>1.413</v>
+      </c>
+      <c r="M182" t="n">
+        <v>0</v>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7737,6 +9777,17 @@
       <c r="H183" t="n">
         <v>1769</v>
       </c>
+      <c r="L183" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="M183" t="n">
+        <v>0</v>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7777,6 +9828,17 @@
       <c r="H184" t="n">
         <v>1253</v>
       </c>
+      <c r="L184" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M184" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7817,6 +9879,17 @@
       <c r="H185" t="n">
         <v>6874</v>
       </c>
+      <c r="L185" t="n">
+        <v>1.476</v>
+      </c>
+      <c r="M185" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7857,6 +9930,17 @@
       <c r="H186" t="n">
         <v>11309</v>
       </c>
+      <c r="L186" t="n">
+        <v>2.614</v>
+      </c>
+      <c r="M186" t="n">
+        <v>0</v>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7897,6 +9981,17 @@
       <c r="H187" t="n">
         <v>323</v>
       </c>
+      <c r="L187" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="M187" t="n">
+        <v>0</v>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7933,6 +10028,17 @@
       <c r="H188" t="n">
         <v>4347</v>
       </c>
+      <c r="L188" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="M188" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="N188" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7973,6 +10079,17 @@
       <c r="H189" t="n">
         <v>2478</v>
       </c>
+      <c r="L189" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="M189" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="N189" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -8009,6 +10126,17 @@
       <c r="H190" t="n">
         <v>0</v>
       </c>
+      <c r="L190" t="n">
+        <v>0</v>
+      </c>
+      <c r="M190" t="n">
+        <v>0</v>
+      </c>
+      <c r="N190" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -8049,6 +10177,17 @@
       <c r="H191" t="n">
         <v>2238</v>
       </c>
+      <c r="L191" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M191" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="N191" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -8089,6 +10228,17 @@
       <c r="H192" t="n">
         <v>5149</v>
       </c>
+      <c r="L192" t="n">
+        <v>1.192</v>
+      </c>
+      <c r="M192" t="n">
+        <v>0</v>
+      </c>
+      <c r="N192" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -8129,6 +10279,17 @@
       <c r="H193" t="n">
         <v>1605</v>
       </c>
+      <c r="L193" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="M193" t="n">
+        <v>0</v>
+      </c>
+      <c r="N193" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
@@ -8169,6 +10330,17 @@
       <c r="H194" s="3" t="n">
         <v>6291</v>
       </c>
+      <c r="L194" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M194" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="N194" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -8209,6 +10381,17 @@
       <c r="H195" s="3" t="n">
         <v>3041</v>
       </c>
+      <c r="L195" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="M195" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="N195" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
@@ -8249,6 +10432,17 @@
       <c r="H196" s="3" t="n">
         <v>6329</v>
       </c>
+      <c r="L196" t="n">
+        <v>1.366</v>
+      </c>
+      <c r="M196" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N196" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
@@ -8289,6 +10483,17 @@
       <c r="H197" s="3" t="n">
         <v>4754</v>
       </c>
+      <c r="L197" t="n">
+        <v>1.106</v>
+      </c>
+      <c r="M197" t="n">
+        <v>0</v>
+      </c>
+      <c r="N197" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -8329,6 +10534,17 @@
       <c r="H198" t="n">
         <v>3211</v>
       </c>
+      <c r="L198" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="M198" t="n">
+        <v>0</v>
+      </c>
+      <c r="N198" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -8369,6 +10585,17 @@
       <c r="H199" t="n">
         <v>550</v>
       </c>
+      <c r="L199" t="n">
+        <v>0.132</v>
+      </c>
+      <c r="M199" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N199" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -8409,6 +10636,17 @@
       <c r="H200" t="n">
         <v>3634</v>
       </c>
+      <c r="L200" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="M200" t="n">
+        <v>0</v>
+      </c>
+      <c r="N200" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -8449,6 +10687,17 @@
       <c r="H201" t="n">
         <v>1798</v>
       </c>
+      <c r="L201" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="M201" t="n">
+        <v>0</v>
+      </c>
+      <c r="N201" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -8489,6 +10738,17 @@
       <c r="H202" t="n">
         <v>4067</v>
       </c>
+      <c r="L202" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M202" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="N202" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -8529,6 +10789,17 @@
       <c r="H203" t="n">
         <v>8034</v>
       </c>
+      <c r="L203" t="n">
+        <v>1.873</v>
+      </c>
+      <c r="M203" t="n">
+        <v>0</v>
+      </c>
+      <c r="N203" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -8569,6 +10840,17 @@
       <c r="H204" t="n">
         <v>22966</v>
       </c>
+      <c r="L204" t="n">
+        <v>4.823</v>
+      </c>
+      <c r="M204" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="N204" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -8609,6 +10891,17 @@
       <c r="H205" t="n">
         <v>2712</v>
       </c>
+      <c r="L205" t="n">
+        <v>0.627</v>
+      </c>
+      <c r="M205" t="n">
+        <v>0</v>
+      </c>
+      <c r="N205" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -8649,6 +10942,17 @@
       <c r="H206" t="n">
         <v>7237</v>
       </c>
+      <c r="L206" t="n">
+        <v>1.687</v>
+      </c>
+      <c r="M206" t="n">
+        <v>0</v>
+      </c>
+      <c r="N206" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -8689,6 +10993,17 @@
       <c r="H207" t="n">
         <v>7030</v>
       </c>
+      <c r="L207" t="n">
+        <v>1.616</v>
+      </c>
+      <c r="M207" t="n">
+        <v>0</v>
+      </c>
+      <c r="N207" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -8729,6 +11044,17 @@
       <c r="H208" t="n">
         <v>12069</v>
       </c>
+      <c r="L208" t="n">
+        <v>2.762</v>
+      </c>
+      <c r="M208" t="n">
+        <v>0</v>
+      </c>
+      <c r="N208" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -8769,6 +11095,17 @@
       <c r="H209" t="n">
         <v>9143</v>
       </c>
+      <c r="L209" t="n">
+        <v>1.978</v>
+      </c>
+      <c r="M209" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="N209" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -8809,6 +11146,17 @@
       <c r="H210" t="n">
         <v>2310</v>
       </c>
+      <c r="L210" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="M210" t="n">
+        <v>0</v>
+      </c>
+      <c r="N210" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -8849,6 +11197,17 @@
       <c r="H211" t="n">
         <v>0</v>
       </c>
+      <c r="L211" t="n">
+        <v>0</v>
+      </c>
+      <c r="M211" t="n">
+        <v>0</v>
+      </c>
+      <c r="N211" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -8889,6 +11248,17 @@
       <c r="H212" t="n">
         <v>2214</v>
       </c>
+      <c r="L212" t="n">
+        <v>0</v>
+      </c>
+      <c r="M212" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="N212" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -8929,6 +11299,17 @@
       <c r="H213" t="n">
         <v>6358</v>
       </c>
+      <c r="L213" t="n">
+        <v>1.277</v>
+      </c>
+      <c r="M213" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="N213" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -8969,6 +11350,17 @@
       <c r="H214" t="n">
         <v>3146</v>
       </c>
+      <c r="L214" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="M214" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N214" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -9009,6 +11401,17 @@
       <c r="H215" t="n">
         <v>4030</v>
       </c>
+      <c r="L215" t="n">
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="M215" t="n">
+        <v>0</v>
+      </c>
+      <c r="N215" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -9049,6 +11452,17 @@
       <c r="H216" t="n">
         <v>4130</v>
       </c>
+      <c r="L216" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="M216" t="n">
+        <v>0</v>
+      </c>
+      <c r="N216" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -9089,6 +11503,17 @@
       <c r="H217" t="n">
         <v>12979</v>
       </c>
+      <c r="L217" t="n">
+        <v>2.329</v>
+      </c>
+      <c r="M217" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N217" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -9129,6 +11554,17 @@
       <c r="H218" t="n">
         <v>4348</v>
       </c>
+      <c r="L218" t="n">
+        <v>1.006</v>
+      </c>
+      <c r="M218" t="n">
+        <v>0</v>
+      </c>
+      <c r="N218" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -9169,6 +11605,17 @@
       <c r="H219" t="n">
         <v>2150</v>
       </c>
+      <c r="L219" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="M219" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="N219" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -9209,6 +11656,17 @@
       <c r="H220" t="n">
         <v>11266</v>
       </c>
+      <c r="L220" t="n">
+        <v>2.619</v>
+      </c>
+      <c r="M220" t="n">
+        <v>0</v>
+      </c>
+      <c r="N220" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -9245,6 +11703,17 @@
       <c r="H221" t="n">
         <v>2998</v>
       </c>
+      <c r="L221" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="M221" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="N221" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
@@ -9285,6 +11754,17 @@
       <c r="H222" s="3" t="n">
         <v>4178</v>
       </c>
+      <c r="L222" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="M222" t="n">
+        <v>0</v>
+      </c>
+      <c r="N222" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
@@ -9325,6 +11805,17 @@
       <c r="H223" s="3" t="n">
         <v>11326</v>
       </c>
+      <c r="L223" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="M223" t="n">
+        <v>0</v>
+      </c>
+      <c r="N223" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -9365,6 +11856,17 @@
       <c r="H224" t="n">
         <v>3637</v>
       </c>
+      <c r="L224" t="n">
+        <v>0</v>
+      </c>
+      <c r="M224" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="N224" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -9405,6 +11907,17 @@
       <c r="H225" t="n">
         <v>2758</v>
       </c>
+      <c r="L225" t="n">
+        <v>0.644</v>
+      </c>
+      <c r="M225" t="n">
+        <v>0</v>
+      </c>
+      <c r="N225" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -9445,6 +11958,17 @@
       <c r="H226" t="n">
         <v>1620</v>
       </c>
+      <c r="L226" t="n">
+        <v>0.376</v>
+      </c>
+      <c r="M226" t="n">
+        <v>0</v>
+      </c>
+      <c r="N226" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -9481,9 +12005,20 @@
       <c r="H227" t="n">
         <v>5998</v>
       </c>
+      <c r="L227" t="n">
+        <v>1.377</v>
+      </c>
+      <c r="M227" t="n">
+        <v>0</v>
+      </c>
+      <c r="N227" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K227"/>
+  <autoFilter ref="A1:N227"/>
   <dataValidations count="2">
     <dataValidation sqref="I2:I227" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Листи!$B$1:$B$2</formula1>
@@ -9502,7 +12037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -9512,6 +12047,9 @@
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9550,6 +12088,21 @@
           <t>Забелешка</t>
         </is>
       </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>Ноќна моќност kW</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>Постојана моќност kW</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>Профил</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -9576,6 +12129,17 @@
         <v>15687</v>
       </c>
       <c r="F2" s="4" t="n"/>
+      <c r="H2" t="n">
+        <v>3.564</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -9602,6 +12166,17 @@
         <v>11088</v>
       </c>
       <c r="F3" s="4" t="n"/>
+      <c r="H3" t="n">
+        <v>2.561</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -9628,6 +12203,17 @@
         <v>7758</v>
       </c>
       <c r="F4" s="4" t="n"/>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.916</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>постојан</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -9654,6 +12240,17 @@
         <v>7626</v>
       </c>
       <c r="F5" s="4" t="n"/>
+      <c r="H5" t="n">
+        <v>1.641</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -9680,6 +12277,17 @@
         <v>5556</v>
       </c>
       <c r="F6" s="4" t="n"/>
+      <c r="H6" t="n">
+        <v>1.234</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -9706,6 +12314,17 @@
         <v>5204</v>
       </c>
       <c r="F7" s="4" t="n"/>
+      <c r="H7" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -9732,6 +12351,17 @@
         <v>4761</v>
       </c>
       <c r="F8" s="4" t="n"/>
+      <c r="H8" t="n">
+        <v>1.063</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -9758,6 +12388,17 @@
         <v>3682</v>
       </c>
       <c r="F9" s="4" t="n"/>
+      <c r="H9" t="n">
+        <v>0.845</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -9784,6 +12425,17 @@
         <v>2460</v>
       </c>
       <c r="F10" s="4" t="n"/>
+      <c r="H10" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ноќен</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -9810,6 +12462,17 @@
         <v>2383</v>
       </c>
       <c r="F11" s="4" t="n"/>
+      <c r="H11" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>мешан</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/analiza-svetilki/izlez/Проверка_мерни_места.xlsx
+++ b/analiza-svetilki/izlez/Проверка_мерни_места.xlsx
@@ -448,7 +448,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -526,38 +526,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Ноќна моќност kW – дел што расте и опаѓа со должината на ноќта (светилки).</t>
+          <t xml:space="preserve">   Зима ÷ лето – колку пати повеќе троши по ден зиме (ноември, февруари) отколку лете (јули, јуни). Кај астрономски часовник е околу 1,5.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Постојана моќност kW – дел што троши и дење, 24 часа (светилки што светат дење или друг потрошувач на ормарот).</t>
+          <t xml:space="preserve">   Профил: „следи ноќта“ (астрономски часовник), „рамен“ (иста потрошувачка секој месец: часовник на фиксни часови или процена на читање), „мешан“.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Профил: ноќен / мешан / постојан. Мерните места со постојан профил веројатно не се само улично осветлување: проверете ги.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Населено место = службено име од списокот на 79 населени места.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Единица = населените места Горно/Долно и Големо/Мало се обединети по основното име; Гарани и Стрелци се заедно.</t>
+          <t xml:space="preserve">   Украсување: броилата на кои светат новогодишните украси (15.12–15.01).</t>
         </is>
       </c>
     </row>
@@ -649,17 +632,17 @@
       </c>
       <c r="L1" s="2" t="inlineStr">
         <is>
-          <t>Ноќна моќност kW</t>
+          <t>Зима ÷ лето (kWh по ден)</t>
         </is>
       </c>
       <c r="M1" s="2" t="inlineStr">
         <is>
-          <t>Постојана моќност kW</t>
+          <t>Профил</t>
         </is>
       </c>
       <c r="N1" s="2" t="inlineStr">
         <is>
-          <t>Профил</t>
+          <t>Украсување</t>
         </is>
       </c>
     </row>
@@ -703,16 +686,14 @@
         <v>2165</v>
       </c>
       <c r="L2" t="n">
-        <v>0.497</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.65</v>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -754,16 +735,14 @@
         <v>479</v>
       </c>
       <c r="L3" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.67</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -805,14 +784,16 @@
         <v>4602</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0.471</v>
+        <v>0.91</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>постојан</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -856,14 +837,16 @@
         <v>3947</v>
       </c>
       <c r="L5" t="n">
-        <v>0.909</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
+        <v>1.56</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>ноќен</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -907,14 +890,16 @@
         <v>16341</v>
       </c>
       <c r="L6" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
+        <v>1.72</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>ноќен</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -958,16 +943,14 @@
         <v>4988</v>
       </c>
       <c r="L7" t="n">
-        <v>1.145</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.56</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1009,16 +992,14 @@
         <v>8073</v>
       </c>
       <c r="L8" t="n">
-        <v>1.764</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.53</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1060,16 +1041,14 @@
         <v>2211</v>
       </c>
       <c r="L9" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>0.96</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1111,16 +1090,14 @@
         <v>3179</v>
       </c>
       <c r="L10" t="n">
-        <v>0.734</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.63</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1162,16 +1139,14 @@
         <v>9014</v>
       </c>
       <c r="L11" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.67</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1213,14 +1188,16 @@
         <v>39</v>
       </c>
       <c r="L12" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>ноќен</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -1264,14 +1241,16 @@
         <v>12145</v>
       </c>
       <c r="L13" t="n">
-        <v>2.767</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
+        <v>1.62</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>ноќен</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -1311,16 +1290,14 @@
         <v>5175</v>
       </c>
       <c r="L14" t="n">
-        <v>0.824</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.158</v>
-      </c>
-      <c r="N14" t="inlineStr">
+        <v>1.28</v>
+      </c>
+      <c r="M14" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1362,16 +1339,14 @@
         <v>3466</v>
       </c>
       <c r="L15" t="n">
-        <v>0.762</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.87</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1413,14 +1388,16 @@
         <v>503</v>
       </c>
       <c r="L16" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
+        <v>1.62</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>ноќен</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -1464,16 +1441,14 @@
         <v>3185</v>
       </c>
       <c r="L17" t="n">
-        <v>0.726</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.64</v>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1515,16 +1490,14 @@
         <v>7863</v>
       </c>
       <c r="L18" t="n">
-        <v>1.621</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.53</v>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1566,16 +1539,14 @@
         <v>4198</v>
       </c>
       <c r="L19" t="n">
-        <v>0.648</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0.151</v>
-      </c>
-      <c r="N19" t="inlineStr">
+        <v>1.53</v>
+      </c>
+      <c r="M19" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1613,16 +1584,14 @@
         <v>3966</v>
       </c>
       <c r="L20" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="M20" t="n">
-        <v>0.412</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>0.97</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1664,16 +1633,14 @@
         <v>3854</v>
       </c>
       <c r="L21" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.67</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1715,16 +1682,14 @@
         <v>3611</v>
       </c>
       <c r="L22" t="n">
-        <v>0.788</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.44</v>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1766,16 +1731,14 @@
         <v>1749</v>
       </c>
       <c r="L23" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="M23" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.46</v>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1817,16 +1780,14 @@
         <v>1397</v>
       </c>
       <c r="L24" t="n">
-        <v>0.323</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.58</v>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1868,16 +1829,14 @@
         <v>2954</v>
       </c>
       <c r="L25" t="n">
-        <v>0.668</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.63</v>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1919,16 +1878,14 @@
         <v>6227</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.589</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1970,16 +1927,14 @@
         <v>2524</v>
       </c>
       <c r="L27" t="n">
-        <v>0.298</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0.149</v>
-      </c>
-      <c r="N27" t="inlineStr">
+        <v>1.46</v>
+      </c>
+      <c r="M27" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2021,16 +1976,14 @@
         <v>9637</v>
       </c>
       <c r="L28" t="n">
-        <v>2.314</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.59</v>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2072,16 +2025,14 @@
         <v>3370</v>
       </c>
       <c r="L29" t="n">
-        <v>0.763</v>
-      </c>
-      <c r="M29" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.67</v>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2123,16 +2074,14 @@
         <v>2984</v>
       </c>
       <c r="L30" t="n">
-        <v>0.681</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2170,16 +2119,14 @@
         <v>3809</v>
       </c>
       <c r="L31" t="n">
-        <v>0.867</v>
-      </c>
-      <c r="M31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.72</v>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2217,16 +2164,14 @@
         <v>2634</v>
       </c>
       <c r="L32" t="n">
-        <v>0.606</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.67</v>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2268,16 +2213,14 @@
         <v>1444</v>
       </c>
       <c r="L33" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>2.11</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2319,16 +2262,14 @@
         <v>5940</v>
       </c>
       <c r="L34" t="n">
-        <v>1.322</v>
-      </c>
-      <c r="M34" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>2.59</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2370,16 +2311,14 @@
         <v>218</v>
       </c>
       <c r="L35" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="M35" t="n">
         <v>0</v>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2421,16 +2360,14 @@
         <v>9599</v>
       </c>
       <c r="L36" t="n">
-        <v>2.042</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.51</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2468,16 +2405,14 @@
         <v>9452</v>
       </c>
       <c r="L37" t="n">
-        <v>1.348</v>
-      </c>
-      <c r="M37" t="n">
-        <v>0.339</v>
-      </c>
-      <c r="N37" t="inlineStr">
+        <v>1.64</v>
+      </c>
+      <c r="M37" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2519,14 +2454,16 @@
         <v>12348</v>
       </c>
       <c r="L38" t="n">
-        <v>2.848</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
+        <v>1.91</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>ноќен</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -2570,16 +2507,14 @@
         <v>3001</v>
       </c>
       <c r="L39" t="n">
-        <v>0.681</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.83</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2617,16 +2552,14 @@
         <v>7740</v>
       </c>
       <c r="L40" t="n">
-        <v>1.647</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.66</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2668,16 +2601,14 @@
         <v>9256</v>
       </c>
       <c r="L41" t="n">
-        <v>2.118</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.59</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2719,16 +2650,14 @@
         <v>804</v>
       </c>
       <c r="L42" t="n">
-        <v>0.185</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.56</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2770,16 +2699,14 @@
         <v>7825</v>
       </c>
       <c r="L43" t="n">
-        <v>1.805</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.62</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2817,16 +2744,14 @@
         <v>5374</v>
       </c>
       <c r="L44" t="n">
-        <v>1.223</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.58</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2864,16 +2789,14 @@
         <v>5414</v>
       </c>
       <c r="L45" t="n">
-        <v>1.159</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.53</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2915,16 +2838,14 @@
         <v>3860</v>
       </c>
       <c r="L46" t="n">
-        <v>0.894</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.95</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2966,16 +2887,14 @@
         <v>6933</v>
       </c>
       <c r="L47" t="n">
-        <v>1.585</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.58</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3017,16 +2936,14 @@
         <v>13867</v>
       </c>
       <c r="L48" t="n">
-        <v>2.888</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>3.23</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3068,16 +2985,14 @@
         <v>1137</v>
       </c>
       <c r="L49" t="n">
-        <v>0.263</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>2.08</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3115,16 +3030,14 @@
         <v>5626</v>
       </c>
       <c r="L50" t="n">
-        <v>1.285</v>
-      </c>
-      <c r="M50" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.69</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3162,16 +3075,14 @@
         <v>6716</v>
       </c>
       <c r="L51" t="n">
-        <v>1.549</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.56</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3213,16 +3124,14 @@
         <v>2049</v>
       </c>
       <c r="L52" t="n">
-        <v>0.472</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.53</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3264,16 +3173,14 @@
         <v>4139</v>
       </c>
       <c r="L53" t="n">
-        <v>0.847</v>
-      </c>
-      <c r="M53" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.51</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3315,16 +3222,14 @@
         <v>1633</v>
       </c>
       <c r="L54" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0.019</v>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.46</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3366,16 +3271,14 @@
         <v>7031</v>
       </c>
       <c r="L55" t="n">
-        <v>1.603</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.58</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3417,14 +3320,16 @@
         <v>4984</v>
       </c>
       <c r="L56" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0.008</v>
+        <v>1.45</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>ноќен</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -3468,14 +3373,16 @@
         <v>4639</v>
       </c>
       <c r="L57" t="n">
-        <v>0.892</v>
-      </c>
-      <c r="M57" t="n">
-        <v>0</v>
+        <v>1.59</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>ноќен</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -3519,16 +3426,14 @@
         <v>1056</v>
       </c>
       <c r="L58" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.112</v>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>1.13</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3570,16 +3475,14 @@
         <v>5678</v>
       </c>
       <c r="L59" t="n">
-        <v>0.624</v>
-      </c>
-      <c r="M59" t="n">
-        <v>0.313</v>
-      </c>
-      <c r="N59" t="inlineStr">
+        <v>1.27</v>
+      </c>
+      <c r="M59" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3621,16 +3524,14 @@
         <v>17618</v>
       </c>
       <c r="L60" t="n">
-        <v>4.008</v>
-      </c>
-      <c r="M60" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.81</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3672,16 +3573,14 @@
         <v>6817</v>
       </c>
       <c r="L61" t="n">
-        <v>1.539</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.69</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3723,16 +3622,14 @@
         <v>6570</v>
       </c>
       <c r="L62" t="n">
-        <v>1.472</v>
-      </c>
-      <c r="M62" t="n">
-        <v>0.021</v>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.51</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -3774,16 +3671,14 @@
         <v>6660</v>
       </c>
       <c r="L63" t="n">
-        <v>1.537</v>
-      </c>
-      <c r="M63" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>2.1</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3825,16 +3720,14 @@
         <v>7678</v>
       </c>
       <c r="L64" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="M64" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.89</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3872,16 +3765,14 @@
         <v>9196</v>
       </c>
       <c r="L65" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="M65" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>2.31</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3919,16 +3810,14 @@
         <v>2967</v>
       </c>
       <c r="L66" t="n">
-        <v>0.678</v>
-      </c>
-      <c r="M66" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.73</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3970,14 +3859,16 @@
         <v>2151</v>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="n">
-        <v>0.234</v>
+        <v>0.7</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>постојан</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -4021,14 +3912,16 @@
         <v>2088</v>
       </c>
       <c r="L68" t="n">
-        <v>0.483</v>
-      </c>
-      <c r="M68" t="n">
-        <v>0</v>
+        <v>2.93</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>ноќен</t>
+          <t>да</t>
         </is>
       </c>
     </row>
@@ -4068,16 +3961,14 @@
         <v>12940</v>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="n">
-        <v>1.283</v>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>0.82</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4119,16 +4010,14 @@
         <v>9350</v>
       </c>
       <c r="L70" t="n">
-        <v>1.603</v>
-      </c>
-      <c r="M70" t="n">
-        <v>0.283</v>
-      </c>
-      <c r="N70" t="inlineStr">
+        <v>1.37</v>
+      </c>
+      <c r="M70" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4166,16 +4055,14 @@
         <v>2887</v>
       </c>
       <c r="L71" t="n">
-        <v>0.338</v>
-      </c>
-      <c r="M71" t="n">
-        <v>0.151</v>
-      </c>
-      <c r="N71" t="inlineStr">
+        <v>1.16</v>
+      </c>
+      <c r="M71" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4217,16 +4104,14 @@
         <v>18595</v>
       </c>
       <c r="L72" t="n">
-        <v>1.587</v>
-      </c>
-      <c r="M72" t="n">
-        <v>1.329</v>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>1.34</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4264,16 +4149,14 @@
         <v>6179</v>
       </c>
       <c r="L73" t="n">
-        <v>1.353</v>
-      </c>
-      <c r="M73" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.7</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4315,16 +4198,14 @@
         <v>65</v>
       </c>
       <c r="L74" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="M74" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="N74" t="inlineStr">
+        <v>0.95</v>
+      </c>
+      <c r="M74" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4366,16 +4247,14 @@
         <v>9335</v>
       </c>
       <c r="L75" t="n">
-        <v>2.155</v>
-      </c>
-      <c r="M75" t="n">
-        <v>0</v>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.57</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4417,16 +4296,14 @@
         <v>1048</v>
       </c>
       <c r="L76" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="M76" t="n">
-        <v>0</v>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4468,16 +4345,14 @@
         <v>5772</v>
       </c>
       <c r="L77" t="n">
-        <v>1.288</v>
-      </c>
-      <c r="M77" t="n">
-        <v>0</v>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.95</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
@@ -4519,16 +4394,14 @@
         <v>2253</v>
       </c>
       <c r="L78" t="n">
-        <v>0.358</v>
-      </c>
-      <c r="M78" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="N78" t="inlineStr">
+        <v>1.47</v>
+      </c>
+      <c r="M78" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
@@ -4570,16 +4443,14 @@
         <v>3771</v>
       </c>
       <c r="L79" t="n">
-        <v>0.869</v>
-      </c>
-      <c r="M79" t="n">
-        <v>0</v>
-      </c>
-      <c r="N79" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.53</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4621,16 +4492,14 @@
         <v>2995</v>
       </c>
       <c r="L80" t="n">
-        <v>0.661</v>
-      </c>
-      <c r="M80" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>2.81</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4672,16 +4541,14 @@
         <v>3642</v>
       </c>
       <c r="L81" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="M81" t="n">
-        <v>0.376</v>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>1.17</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4723,16 +4590,14 @@
         <v>3941</v>
       </c>
       <c r="L82" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.57</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4774,16 +4639,14 @@
         <v>5281</v>
       </c>
       <c r="L83" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="M83" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>2.31</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4825,16 +4688,14 @@
         <v>2688</v>
       </c>
       <c r="L84" t="n">
-        <v>0.579</v>
-      </c>
-      <c r="M84" t="n">
-        <v>0.014</v>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4876,16 +4737,14 @@
         <v>6967</v>
       </c>
       <c r="L85" t="n">
-        <v>1.611</v>
-      </c>
-      <c r="M85" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.59</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4927,16 +4786,14 @@
         <v>6460</v>
       </c>
       <c r="L86" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="M86" t="n">
-        <v>0</v>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.66</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4978,16 +4835,14 @@
         <v>7856</v>
       </c>
       <c r="L87" t="n">
-        <v>1.788</v>
-      </c>
-      <c r="M87" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.59</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5025,16 +4880,14 @@
         <v>12365</v>
       </c>
       <c r="L88" t="n">
-        <v>2.184</v>
-      </c>
-      <c r="M88" t="n">
-        <v>0.321</v>
-      </c>
-      <c r="N88" t="inlineStr">
+        <v>1.29</v>
+      </c>
+      <c r="M88" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5076,16 +4929,14 @@
         <v>2483</v>
       </c>
       <c r="L89" t="n">
-        <v>0.053</v>
-      </c>
-      <c r="M89" t="n">
-        <v>0.242</v>
-      </c>
-      <c r="N89" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>1.21</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5127,16 +4978,14 @@
         <v>1336</v>
       </c>
       <c r="L90" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="M90" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5178,16 +5027,14 @@
         <v>576</v>
       </c>
       <c r="L91" t="n">
-        <v>0.134</v>
-      </c>
-      <c r="M91" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.53</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5225,16 +5072,14 @@
         <v>4979</v>
       </c>
       <c r="L92" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="M92" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>2.48</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5276,16 +5121,14 @@
         <v>1271</v>
       </c>
       <c r="L93" t="n">
-        <v>0.273</v>
-      </c>
-      <c r="M93" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="N93" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.48</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5327,16 +5170,14 @@
         <v>867</v>
       </c>
       <c r="L94" t="n">
-        <v>0.218</v>
-      </c>
-      <c r="M94" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.71</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5378,16 +5219,14 @@
         <v>1994</v>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
-      </c>
-      <c r="M95" t="n">
-        <v>0.243</v>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>0.83</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="3" t="inlineStr">
@@ -5429,16 +5268,14 @@
         <v>2743</v>
       </c>
       <c r="L96" t="n">
-        <v>0.613</v>
-      </c>
-      <c r="M96" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.65</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5480,16 +5317,14 @@
         <v>5506</v>
       </c>
       <c r="L97" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="M97" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="N97" t="inlineStr">
+        <v>1.38</v>
+      </c>
+      <c r="M97" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5531,16 +5366,14 @@
         <v>297</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>0.93</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5582,16 +5415,14 @@
         <v>2365</v>
       </c>
       <c r="L99" t="n">
-        <v>0.493</v>
-      </c>
-      <c r="M99" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="N99" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.4</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5633,16 +5464,14 @@
         <v>1370</v>
       </c>
       <c r="L100" t="n">
-        <v>0.253</v>
-      </c>
-      <c r="M100" t="n">
-        <v>0.031</v>
-      </c>
-      <c r="N100" t="inlineStr">
+        <v>1.34</v>
+      </c>
+      <c r="M100" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5684,16 +5513,14 @@
         <v>2879</v>
       </c>
       <c r="L101" t="n">
-        <v>0.483</v>
-      </c>
-      <c r="M101" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="N101" t="inlineStr">
+        <v>1.29</v>
+      </c>
+      <c r="M101" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5735,16 +5562,14 @@
         <v>4277</v>
       </c>
       <c r="L102" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="M102" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.51</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5786,16 +5611,14 @@
         <v>3764</v>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5837,16 +5660,14 @@
         <v>3192</v>
       </c>
       <c r="L104" t="n">
-        <v>0.624</v>
-      </c>
-      <c r="M104" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="N104" t="inlineStr">
+        <v>1.02</v>
+      </c>
+      <c r="M104" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5888,16 +5709,14 @@
         <v>2732</v>
       </c>
       <c r="L105" t="n">
-        <v>0.594</v>
-      </c>
-      <c r="M105" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>2.44</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5939,16 +5758,14 @@
         <v>1246</v>
       </c>
       <c r="L106" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>1.09</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5986,16 +5803,14 @@
         <v>1673</v>
       </c>
       <c r="L107" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="M107" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="N107" t="inlineStr">
+        <v>1.28</v>
+      </c>
+      <c r="M107" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6033,16 +5848,14 @@
         <v>3737</v>
       </c>
       <c r="L108" t="n">
-        <v>0.855</v>
-      </c>
-      <c r="M108" t="n">
-        <v>0</v>
-      </c>
-      <c r="N108" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.67</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6080,16 +5893,14 @@
         <v>895</v>
       </c>
       <c r="L109" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M109" t="n">
-        <v>0.07099999999999999</v>
-      </c>
-      <c r="N109" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>1.97</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6131,16 +5942,14 @@
         <v>4912</v>
       </c>
       <c r="L110" t="n">
-        <v>0.836</v>
-      </c>
-      <c r="M110" t="n">
-        <v>0.139</v>
-      </c>
-      <c r="N110" t="inlineStr">
+        <v>1.31</v>
+      </c>
+      <c r="M110" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6182,16 +5991,14 @@
         <v>2090</v>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
-      </c>
-      <c r="M111" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="N111" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>1.03</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6233,16 +6040,14 @@
         <v>1411</v>
       </c>
       <c r="L112" t="n">
-        <v>0.328</v>
-      </c>
-      <c r="M112" t="n">
-        <v>0</v>
-      </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.48</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6284,16 +6089,14 @@
         <v>460</v>
       </c>
       <c r="L113" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="M113" t="n">
-        <v>0</v>
-      </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.32</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -6335,16 +6138,14 @@
         <v>2649</v>
       </c>
       <c r="L114" t="n">
-        <v>0.614</v>
-      </c>
-      <c r="M114" t="n">
-        <v>0</v>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>2.64</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6386,16 +6187,14 @@
         <v>2998</v>
       </c>
       <c r="L115" t="n">
-        <v>0.289</v>
-      </c>
-      <c r="M115" t="n">
-        <v>0.196</v>
-      </c>
-      <c r="N115" t="inlineStr">
+        <v>1.2</v>
+      </c>
+      <c r="M115" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
@@ -6437,16 +6236,14 @@
         <v>2399</v>
       </c>
       <c r="L116" t="n">
-        <v>0.578</v>
-      </c>
-      <c r="M116" t="n">
-        <v>0</v>
-      </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>2.68</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6488,16 +6285,14 @@
         <v>4225</v>
       </c>
       <c r="L117" t="n">
-        <v>0.9379999999999999</v>
-      </c>
-      <c r="M117" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="N117" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.38</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -6535,16 +6330,14 @@
         <v>3797</v>
       </c>
       <c r="L118" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="M118" t="n">
-        <v>0.279</v>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>1.16</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6586,16 +6379,14 @@
         <v>2776</v>
       </c>
       <c r="L119" t="n">
-        <v>0.636</v>
-      </c>
-      <c r="M119" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.52</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="3" t="inlineStr">
@@ -6637,16 +6428,14 @@
         <v>3457</v>
       </c>
       <c r="L120" t="n">
-        <v>0.593</v>
-      </c>
-      <c r="M120" t="n">
-        <v>0</v>
-      </c>
-      <c r="N120" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>0.73</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6688,16 +6477,14 @@
         <v>2384</v>
       </c>
       <c r="L121" t="n">
-        <v>0.507</v>
-      </c>
-      <c r="M121" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.37</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6741,14 +6528,12 @@
       <c r="L122" t="n">
         <v>0</v>
       </c>
-      <c r="M122" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6786,16 +6571,14 @@
         <v>2919</v>
       </c>
       <c r="L123" t="n">
-        <v>0.6830000000000001</v>
-      </c>
-      <c r="M123" t="n">
-        <v>0</v>
-      </c>
-      <c r="N123" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>2.55</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6833,16 +6616,14 @@
         <v>6676</v>
       </c>
       <c r="L124" t="n">
-        <v>1.523</v>
-      </c>
-      <c r="M124" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="N124" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6884,16 +6665,14 @@
         <v>10431</v>
       </c>
       <c r="L125" t="n">
-        <v>2.421</v>
-      </c>
-      <c r="M125" t="n">
-        <v>0</v>
-      </c>
-      <c r="N125" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.67</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6935,16 +6714,14 @@
         <v>4014</v>
       </c>
       <c r="L126" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="M126" t="n">
-        <v>0.017</v>
-      </c>
-      <c r="N126" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.56</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6982,16 +6759,14 @@
         <v>2614</v>
       </c>
       <c r="L127" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="M127" t="n">
-        <v>0.286</v>
-      </c>
-      <c r="N127" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>1.1</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -7033,16 +6808,14 @@
         <v>3700</v>
       </c>
       <c r="L128" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="M128" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="N128" t="inlineStr">
+        <v>1.52</v>
+      </c>
+      <c r="M128" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -7084,16 +6857,14 @@
         <v>3062</v>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
-      </c>
-      <c r="M129" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="N129" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>0.27</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -7131,16 +6902,14 @@
         <v>7507</v>
       </c>
       <c r="L130" t="n">
-        <v>1.441</v>
-      </c>
-      <c r="M130" t="n">
-        <v>0.151</v>
-      </c>
-      <c r="N130" t="inlineStr">
+        <v>1.4</v>
+      </c>
+      <c r="M130" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -7182,16 +6951,14 @@
         <v>1287</v>
       </c>
       <c r="L131" t="n">
-        <v>0.261</v>
-      </c>
-      <c r="M131" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="N131" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.45</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -7233,16 +7000,14 @@
         <v>4880</v>
       </c>
       <c r="L132" t="n">
-        <v>1.117</v>
-      </c>
-      <c r="M132" t="n">
-        <v>0</v>
-      </c>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.67</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -7284,16 +7049,14 @@
         <v>2110</v>
       </c>
       <c r="L133" t="n">
-        <v>0.489</v>
-      </c>
-      <c r="M133" t="n">
-        <v>0</v>
-      </c>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.91</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -7335,16 +7098,14 @@
         <v>3667</v>
       </c>
       <c r="L134" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="M134" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.53</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -7382,16 +7143,14 @@
         <v>2019</v>
       </c>
       <c r="L135" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="M135" t="n">
-        <v>0</v>
-      </c>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.62</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -7433,16 +7192,14 @@
         <v>2601</v>
       </c>
       <c r="L136" t="n">
-        <v>0.326</v>
-      </c>
-      <c r="M136" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="N136" t="inlineStr">
+        <v>1.4</v>
+      </c>
+      <c r="M136" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -7480,16 +7237,14 @@
         <v>933</v>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
-      </c>
-      <c r="M137" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>0.73</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -7527,16 +7282,14 @@
         <v>6684</v>
       </c>
       <c r="L138" t="n">
-        <v>1.202</v>
-      </c>
-      <c r="M138" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="N138" t="inlineStr">
+        <v>1.4</v>
+      </c>
+      <c r="M138" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -7574,16 +7327,14 @@
         <v>13152</v>
       </c>
       <c r="L139" t="n">
-        <v>2.762</v>
-      </c>
-      <c r="M139" t="n">
-        <v>0</v>
-      </c>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>5.73</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -7625,16 +7376,14 @@
         <v>7006</v>
       </c>
       <c r="L140" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="M140" t="n">
-        <v>0</v>
-      </c>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>2.05</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -7676,16 +7425,14 @@
         <v>6410</v>
       </c>
       <c r="L141" t="n">
-        <v>1.438</v>
-      </c>
-      <c r="M141" t="n">
-        <v>0</v>
-      </c>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.68</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -7727,16 +7474,14 @@
         <v>13487</v>
       </c>
       <c r="L142" t="n">
-        <v>2.557</v>
-      </c>
-      <c r="M142" t="n">
-        <v>0.271</v>
-      </c>
-      <c r="N142" t="inlineStr">
+        <v>1.48</v>
+      </c>
+      <c r="M142" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -7778,16 +7523,14 @@
         <v>3326</v>
       </c>
       <c r="L143" t="n">
-        <v>0.621</v>
-      </c>
-      <c r="M143" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="N143" t="inlineStr">
+        <v>1.5</v>
+      </c>
+      <c r="M143" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -7829,16 +7572,14 @@
         <v>12237</v>
       </c>
       <c r="L144" t="n">
-        <v>2.535</v>
-      </c>
-      <c r="M144" t="n">
-        <v>0.124</v>
-      </c>
-      <c r="N144" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.54</v>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -7880,16 +7621,14 @@
         <v>2411</v>
       </c>
       <c r="L145" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="M145" t="n">
-        <v>0.041</v>
-      </c>
-      <c r="N145" t="inlineStr">
+        <v>1.51</v>
+      </c>
+      <c r="M145" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -7931,16 +7670,14 @@
         <v>1330</v>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
-      </c>
-      <c r="M146" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>0.82</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -7982,16 +7719,14 @@
         <v>7047</v>
       </c>
       <c r="L147" t="n">
-        <v>1.445</v>
-      </c>
-      <c r="M147" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="N147" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.51</v>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -8033,16 +7768,14 @@
         <v>4285</v>
       </c>
       <c r="L148" t="n">
-        <v>0.984</v>
-      </c>
-      <c r="M148" t="n">
-        <v>0</v>
-      </c>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.69</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -8084,16 +7817,14 @@
         <v>4250</v>
       </c>
       <c r="L149" t="n">
-        <v>0.949</v>
-      </c>
-      <c r="M149" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.56</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -8131,16 +7862,14 @@
         <v>7162</v>
       </c>
       <c r="L150" t="n">
-        <v>1.545</v>
-      </c>
-      <c r="M150" t="n">
-        <v>0.047</v>
-      </c>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.59</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -8182,16 +7911,14 @@
         <v>8192</v>
       </c>
       <c r="L151" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="M151" t="n">
-        <v>0</v>
-      </c>
-      <c r="N151" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.57</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -8233,16 +7960,14 @@
         <v>4182</v>
       </c>
       <c r="L152" t="n">
-        <v>0.881</v>
-      </c>
-      <c r="M152" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="N152" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.46</v>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -8286,14 +8011,12 @@
       <c r="L153" t="n">
         <v>0</v>
       </c>
-      <c r="M153" t="n">
-        <v>0</v>
-      </c>
-      <c r="N153" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -8335,16 +8058,14 @@
         <v>6257</v>
       </c>
       <c r="L154" t="n">
-        <v>1.452</v>
-      </c>
-      <c r="M154" t="n">
-        <v>0</v>
-      </c>
-      <c r="N154" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.54</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -8386,16 +8107,14 @@
         <v>8012</v>
       </c>
       <c r="L155" t="n">
-        <v>1.692</v>
-      </c>
-      <c r="M155" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.45</v>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -8437,16 +8156,14 @@
         <v>541</v>
       </c>
       <c r="L156" t="n">
-        <v>0.121</v>
-      </c>
-      <c r="M156" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="N156" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.51</v>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -8484,16 +8201,14 @@
         <v>2148</v>
       </c>
       <c r="L157" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="M157" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>0.74</v>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -8535,16 +8250,14 @@
         <v>3956</v>
       </c>
       <c r="L158" t="n">
-        <v>0.916</v>
-      </c>
-      <c r="M158" t="n">
-        <v>0</v>
-      </c>
-      <c r="N158" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.57</v>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" s="3" t="inlineStr">
@@ -8586,16 +8299,14 @@
         <v>2752</v>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
-      </c>
-      <c r="M159" t="n">
-        <v>0.384</v>
-      </c>
-      <c r="N159" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>1.58</v>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -8637,16 +8348,14 @@
         <v>2409</v>
       </c>
       <c r="L160" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="M160" t="n">
-        <v>0</v>
-      </c>
-      <c r="N160" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -8688,16 +8397,14 @@
         <v>5037</v>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
-      </c>
-      <c r="M161" t="n">
-        <v>0.553</v>
-      </c>
-      <c r="N161" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>0.9</v>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -8735,16 +8442,14 @@
         <v>1731</v>
       </c>
       <c r="L162" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="M162" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="N162" t="inlineStr">
+        <v>1.19</v>
+      </c>
+      <c r="M162" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -8782,16 +8487,14 @@
         <v>4109</v>
       </c>
       <c r="L163" t="n">
-        <v>0.947</v>
-      </c>
-      <c r="M163" t="n">
-        <v>0</v>
-      </c>
-      <c r="N163" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.51</v>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -8835,14 +8538,12 @@
       <c r="L164" t="n">
         <v>0</v>
       </c>
-      <c r="M164" t="n">
-        <v>0.116</v>
-      </c>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -8884,16 +8585,14 @@
         <v>437</v>
       </c>
       <c r="L165" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="M165" t="n">
-        <v>0</v>
-      </c>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.88</v>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -8937,14 +8636,12 @@
       <c r="L166" t="n">
         <v>0</v>
       </c>
-      <c r="M166" t="n">
-        <v>0</v>
-      </c>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -8982,16 +8679,14 @@
         <v>369</v>
       </c>
       <c r="L167" t="n">
-        <v>0.08599999999999999</v>
-      </c>
-      <c r="M167" t="n">
-        <v>0</v>
-      </c>
-      <c r="N167" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>2.12</v>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -9033,16 +8728,14 @@
         <v>1091</v>
       </c>
       <c r="L168" t="n">
-        <v>0.233</v>
-      </c>
-      <c r="M168" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.37</v>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -9084,16 +8777,14 @@
         <v>3825</v>
       </c>
       <c r="L169" t="n">
-        <v>0.792</v>
-      </c>
-      <c r="M169" t="n">
-        <v>0.046</v>
-      </c>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.34</v>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -9135,16 +8826,14 @@
         <v>1529</v>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
-      </c>
-      <c r="M170" t="n">
-        <v>0.154</v>
-      </c>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>0.99</v>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -9186,16 +8875,14 @@
         <v>8</v>
       </c>
       <c r="L171" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="M171" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>1.05</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -9237,16 +8924,14 @@
         <v>332</v>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
-      </c>
-      <c r="M172" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>1.03</v>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -9284,16 +8969,14 @@
         <v>680</v>
       </c>
       <c r="L173" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="M173" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="N173" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.49</v>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -9331,16 +9014,14 @@
         <v>538</v>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
-      </c>
-      <c r="M174" t="n">
-        <v>0.061</v>
-      </c>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>0.7</v>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -9382,16 +9063,14 @@
         <v>155</v>
       </c>
       <c r="L175" t="n">
-        <v>0.036</v>
-      </c>
-      <c r="M175" t="n">
-        <v>0</v>
-      </c>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.24</v>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -9429,16 +9108,14 @@
         <v>760</v>
       </c>
       <c r="L176" t="n">
-        <v>0.177</v>
-      </c>
-      <c r="M176" t="n">
-        <v>0</v>
-      </c>
-      <c r="N176" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>3.65</v>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -9480,16 +9157,14 @@
         <v>4858</v>
       </c>
       <c r="L177" t="n">
-        <v>0.926</v>
-      </c>
-      <c r="M177" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="N177" t="inlineStr">
+        <v>1.34</v>
+      </c>
+      <c r="M177" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -9527,16 +9202,14 @@
         <v>3834</v>
       </c>
       <c r="L178" t="n">
-        <v>0.681</v>
-      </c>
-      <c r="M178" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="N178" t="inlineStr">
+        <v>1.34</v>
+      </c>
+      <c r="M178" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -9578,16 +9251,14 @@
         <v>3769</v>
       </c>
       <c r="L179" t="n">
-        <v>0.6860000000000001</v>
-      </c>
-      <c r="M179" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="N179" t="inlineStr">
+        <v>1.32</v>
+      </c>
+      <c r="M179" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -9629,16 +9300,14 @@
         <v>4502</v>
       </c>
       <c r="L180" t="n">
-        <v>0.877</v>
-      </c>
-      <c r="M180" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="N180" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.36</v>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -9680,16 +9349,14 @@
         <v>10204</v>
       </c>
       <c r="L181" t="n">
-        <v>2.369</v>
-      </c>
-      <c r="M181" t="n">
-        <v>0</v>
-      </c>
-      <c r="N181" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.66</v>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -9727,16 +9394,14 @@
         <v>6117</v>
       </c>
       <c r="L182" t="n">
-        <v>1.413</v>
-      </c>
-      <c r="M182" t="n">
-        <v>0</v>
-      </c>
-      <c r="N182" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.55</v>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -9778,16 +9443,14 @@
         <v>1769</v>
       </c>
       <c r="L183" t="n">
-        <v>0.407</v>
-      </c>
-      <c r="M183" t="n">
-        <v>0</v>
-      </c>
-      <c r="N183" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.58</v>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -9829,16 +9492,14 @@
         <v>1253</v>
       </c>
       <c r="L184" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="M184" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="N184" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.45</v>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -9880,16 +9541,14 @@
         <v>6874</v>
       </c>
       <c r="L185" t="n">
-        <v>1.476</v>
-      </c>
-      <c r="M185" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="N185" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.49</v>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -9931,16 +9590,14 @@
         <v>11309</v>
       </c>
       <c r="L186" t="n">
-        <v>2.614</v>
-      </c>
-      <c r="M186" t="n">
-        <v>0</v>
-      </c>
-      <c r="N186" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.57</v>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -9982,16 +9639,14 @@
         <v>323</v>
       </c>
       <c r="L187" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="M187" t="n">
-        <v>0</v>
-      </c>
-      <c r="N187" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>43.31</v>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -10029,16 +9684,14 @@
         <v>4347</v>
       </c>
       <c r="L188" t="n">
-        <v>0.882</v>
-      </c>
-      <c r="M188" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="N188" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.48</v>
+      </c>
+      <c r="M188" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -10080,16 +9733,14 @@
         <v>2478</v>
       </c>
       <c r="L189" t="n">
-        <v>0.468</v>
-      </c>
-      <c r="M189" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="N189" t="inlineStr">
+        <v>1.4</v>
+      </c>
+      <c r="M189" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -10126,17 +9777,12 @@
       <c r="H190" t="n">
         <v>0</v>
       </c>
-      <c r="L190" t="n">
-        <v>0</v>
-      </c>
-      <c r="M190" t="n">
-        <v>0</v>
-      </c>
-      <c r="N190" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+      <c r="M190" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -10178,16 +9824,14 @@
         <v>2238</v>
       </c>
       <c r="L191" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="M191" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="N191" t="inlineStr">
+        <v>1.18</v>
+      </c>
+      <c r="M191" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -10229,16 +9873,14 @@
         <v>5149</v>
       </c>
       <c r="L192" t="n">
-        <v>1.192</v>
-      </c>
-      <c r="M192" t="n">
-        <v>0</v>
-      </c>
-      <c r="N192" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.54</v>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -10280,16 +9922,14 @@
         <v>1605</v>
       </c>
       <c r="L193" t="n">
-        <v>0.371</v>
-      </c>
-      <c r="M193" t="n">
-        <v>0</v>
-      </c>
-      <c r="N193" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>2.47</v>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="3" t="inlineStr">
@@ -10331,16 +9971,14 @@
         <v>6291</v>
       </c>
       <c r="L194" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M194" t="n">
-        <v>0.066</v>
-      </c>
-      <c r="N194" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.43</v>
+      </c>
+      <c r="M194" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="3" t="inlineStr">
@@ -10382,16 +10020,14 @@
         <v>3041</v>
       </c>
       <c r="L195" t="n">
-        <v>0.526</v>
-      </c>
-      <c r="M195" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="N195" t="inlineStr">
+        <v>1.42</v>
+      </c>
+      <c r="M195" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="3" t="inlineStr">
@@ -10433,16 +10069,14 @@
         <v>6329</v>
       </c>
       <c r="L196" t="n">
-        <v>1.366</v>
-      </c>
-      <c r="M196" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="N196" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.55</v>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="3" t="inlineStr">
@@ -10484,16 +10118,14 @@
         <v>4754</v>
       </c>
       <c r="L197" t="n">
-        <v>1.106</v>
-      </c>
-      <c r="M197" t="n">
-        <v>0</v>
-      </c>
-      <c r="N197" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.52</v>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -10535,16 +10167,14 @@
         <v>3211</v>
       </c>
       <c r="L198" t="n">
-        <v>0.736</v>
-      </c>
-      <c r="M198" t="n">
-        <v>0</v>
-      </c>
-      <c r="N198" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.62</v>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -10586,16 +10216,14 @@
         <v>550</v>
       </c>
       <c r="L199" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="M199" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="N199" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.23</v>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -10637,16 +10265,14 @@
         <v>3634</v>
       </c>
       <c r="L200" t="n">
-        <v>0.848</v>
-      </c>
-      <c r="M200" t="n">
-        <v>0</v>
-      </c>
-      <c r="N200" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.56</v>
+      </c>
+      <c r="M200" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -10688,16 +10314,14 @@
         <v>1798</v>
       </c>
       <c r="L201" t="n">
-        <v>0.416</v>
-      </c>
-      <c r="M201" t="n">
-        <v>0</v>
-      </c>
-      <c r="N201" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.92</v>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -10739,16 +10363,14 @@
         <v>4067</v>
       </c>
       <c r="L202" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="M202" t="n">
-        <v>0.329</v>
-      </c>
-      <c r="N202" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>1.24</v>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -10790,16 +10412,14 @@
         <v>8034</v>
       </c>
       <c r="L203" t="n">
-        <v>1.873</v>
-      </c>
-      <c r="M203" t="n">
-        <v>0</v>
-      </c>
-      <c r="N203" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.56</v>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -10841,16 +10461,14 @@
         <v>22966</v>
       </c>
       <c r="L204" t="n">
-        <v>4.823</v>
-      </c>
-      <c r="M204" t="n">
-        <v>0.412</v>
-      </c>
-      <c r="N204" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>0.99</v>
+      </c>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -10892,16 +10510,14 @@
         <v>2712</v>
       </c>
       <c r="L205" t="n">
-        <v>0.627</v>
-      </c>
-      <c r="M205" t="n">
-        <v>0</v>
-      </c>
-      <c r="N205" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.55</v>
+      </c>
+      <c r="M205" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -10943,16 +10559,14 @@
         <v>7237</v>
       </c>
       <c r="L206" t="n">
-        <v>1.687</v>
-      </c>
-      <c r="M206" t="n">
-        <v>0</v>
-      </c>
-      <c r="N206" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>2.09</v>
+      </c>
+      <c r="M206" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -10994,16 +10608,14 @@
         <v>7030</v>
       </c>
       <c r="L207" t="n">
-        <v>1.616</v>
-      </c>
-      <c r="M207" t="n">
-        <v>0</v>
-      </c>
-      <c r="N207" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.8</v>
+      </c>
+      <c r="M207" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -11045,16 +10657,14 @@
         <v>12069</v>
       </c>
       <c r="L208" t="n">
-        <v>2.762</v>
-      </c>
-      <c r="M208" t="n">
-        <v>0</v>
-      </c>
-      <c r="N208" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.89</v>
+      </c>
+      <c r="M208" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -11096,16 +10706,14 @@
         <v>9143</v>
       </c>
       <c r="L209" t="n">
-        <v>1.978</v>
-      </c>
-      <c r="M209" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="N209" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.78</v>
+      </c>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -11147,16 +10755,14 @@
         <v>2310</v>
       </c>
       <c r="L210" t="n">
-        <v>0.533</v>
-      </c>
-      <c r="M210" t="n">
-        <v>0</v>
-      </c>
-      <c r="N210" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>2.33</v>
+      </c>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -11197,17 +10803,12 @@
       <c r="H211" t="n">
         <v>0</v>
       </c>
-      <c r="L211" t="n">
-        <v>0</v>
-      </c>
-      <c r="M211" t="n">
-        <v>0</v>
-      </c>
-      <c r="N211" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+      <c r="M211" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -11249,16 +10850,14 @@
         <v>2214</v>
       </c>
       <c r="L212" t="n">
-        <v>0</v>
-      </c>
-      <c r="M212" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="N212" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>0.12</v>
+      </c>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -11300,16 +10899,14 @@
         <v>6358</v>
       </c>
       <c r="L213" t="n">
-        <v>1.277</v>
-      </c>
-      <c r="M213" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="N213" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.44</v>
+      </c>
+      <c r="M213" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -11351,16 +10948,14 @@
         <v>3146</v>
       </c>
       <c r="L214" t="n">
-        <v>0.711</v>
-      </c>
-      <c r="M214" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="N214" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.53</v>
+      </c>
+      <c r="M214" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -11402,16 +10997,14 @@
         <v>4030</v>
       </c>
       <c r="L215" t="n">
-        <v>0.9350000000000001</v>
-      </c>
-      <c r="M215" t="n">
-        <v>0</v>
-      </c>
-      <c r="N215" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.81</v>
+      </c>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -11453,16 +11046,14 @@
         <v>4130</v>
       </c>
       <c r="L216" t="n">
-        <v>0.957</v>
-      </c>
-      <c r="M216" t="n">
-        <v>0</v>
-      </c>
-      <c r="N216" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.59</v>
+      </c>
+      <c r="M216" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -11504,16 +11095,14 @@
         <v>12979</v>
       </c>
       <c r="L217" t="n">
-        <v>2.329</v>
-      </c>
-      <c r="M217" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="N217" t="inlineStr">
+        <v>1.36</v>
+      </c>
+      <c r="M217" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="N217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -11555,16 +11144,14 @@
         <v>4348</v>
       </c>
       <c r="L218" t="n">
-        <v>1.006</v>
-      </c>
-      <c r="M218" t="n">
-        <v>0</v>
-      </c>
-      <c r="N218" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="M218" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -11606,16 +11193,14 @@
         <v>2150</v>
       </c>
       <c r="L219" t="n">
-        <v>0.454</v>
-      </c>
-      <c r="M219" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="N219" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.51</v>
+      </c>
+      <c r="M219" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -11657,16 +11242,14 @@
         <v>11266</v>
       </c>
       <c r="L220" t="n">
-        <v>2.619</v>
-      </c>
-      <c r="M220" t="n">
-        <v>0</v>
-      </c>
-      <c r="N220" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>2.93</v>
+      </c>
+      <c r="M220" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -11704,16 +11287,14 @@
         <v>2998</v>
       </c>
       <c r="L221" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="M221" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="N221" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="M221" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="3" t="inlineStr">
@@ -11755,16 +11336,14 @@
         <v>4178</v>
       </c>
       <c r="L222" t="n">
-        <v>0.952</v>
-      </c>
-      <c r="M222" t="n">
-        <v>0</v>
-      </c>
-      <c r="N222" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.78</v>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="3" t="inlineStr">
@@ -11806,16 +11385,14 @@
         <v>11326</v>
       </c>
       <c r="L223" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="M223" t="n">
-        <v>0</v>
-      </c>
-      <c r="N223" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -11857,16 +11434,14 @@
         <v>3637</v>
       </c>
       <c r="L224" t="n">
-        <v>0</v>
-      </c>
-      <c r="M224" t="n">
-        <v>0.431</v>
-      </c>
-      <c r="N224" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="N224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -11908,16 +11483,14 @@
         <v>2758</v>
       </c>
       <c r="L225" t="n">
-        <v>0.644</v>
-      </c>
-      <c r="M225" t="n">
-        <v>0</v>
-      </c>
-      <c r="N225" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.46</v>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -11959,16 +11532,14 @@
         <v>1620</v>
       </c>
       <c r="L226" t="n">
-        <v>0.376</v>
-      </c>
-      <c r="M226" t="n">
-        <v>0</v>
-      </c>
-      <c r="N226" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.64</v>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -12006,16 +11577,14 @@
         <v>5998</v>
       </c>
       <c r="L227" t="n">
-        <v>1.377</v>
-      </c>
-      <c r="M227" t="n">
-        <v>0</v>
-      </c>
-      <c r="N227" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.72</v>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="N227" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N227"/>
@@ -12090,17 +11659,17 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>Ноќна моќност kW</t>
+          <t>Зима ÷ лето (kWh по ден)</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
         <is>
-          <t>Постојана моќност kW</t>
+          <t>Профил</t>
         </is>
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>Профил</t>
+          <t>Украсување</t>
         </is>
       </c>
     </row>
@@ -12130,16 +11699,14 @@
       </c>
       <c r="F2" s="4" t="n"/>
       <c r="H2" t="n">
-        <v>3.564</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.48</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -12167,16 +11734,14 @@
       </c>
       <c r="F3" s="4" t="n"/>
       <c r="H3" t="n">
-        <v>2.561</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.51</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -12204,16 +11769,14 @@
       </c>
       <c r="F4" s="4" t="n"/>
       <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0.916</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>постојан</t>
-        </is>
-      </c>
+        <v>0.71</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>рамен</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -12241,16 +11804,14 @@
       </c>
       <c r="F5" s="4" t="n"/>
       <c r="H5" t="n">
-        <v>1.641</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.067</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.55</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -12278,16 +11839,14 @@
       </c>
       <c r="F6" s="4" t="n"/>
       <c r="H6" t="n">
-        <v>1.234</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.83</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -12315,16 +11874,14 @@
       </c>
       <c r="F7" s="4" t="n"/>
       <c r="H7" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.6</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -12352,16 +11909,14 @@
       </c>
       <c r="F8" s="4" t="n"/>
       <c r="H8" t="n">
-        <v>1.063</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.61</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -12389,16 +11944,14 @@
       </c>
       <c r="F9" s="4" t="n"/>
       <c r="H9" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="I9" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.72</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -12426,16 +11979,14 @@
       </c>
       <c r="F10" s="4" t="n"/>
       <c r="H10" t="n">
-        <v>0.5659999999999999</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>ноќен</t>
-        </is>
-      </c>
+        <v>1.51</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>следи ноќта</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -12463,16 +12014,14 @@
       </c>
       <c r="F11" s="4" t="n"/>
       <c r="H11" t="n">
-        <v>0.322</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="J11" t="inlineStr">
+        <v>1.23</v>
+      </c>
+      <c r="I11" t="inlineStr">
         <is>
           <t>мешан</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
